--- a/sources/table_normalization/xlsx/environment-table41.xlsx
+++ b/sources/table_normalization/xlsx/environment-table41.xlsx
@@ -243,7 +243,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -261,7 +261,6 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -744,8 +743,8 @@
   <cols>
     <col min="1" max="4" width="13" style="1"/>
     <col min="5" max="5" width="24.08984375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="44.6328125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="31.81640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="35.90625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="21.81640625" style="1" customWidth="1"/>
     <col min="8" max="8" width="25.6328125" style="1" customWidth="1"/>
     <col min="9" max="16384" width="13" style="1"/>
   </cols>
@@ -1007,9 +1006,9 @@
       <c r="A12" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
       <c r="E12" s="4">
         <f t="shared" ref="E12:G12" si="0">AVERAGE(E2:E11)</f>
         <v>109.83</v>
@@ -1028,9 +1027,9 @@
       <c r="A13" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
       <c r="E13" s="4">
         <f t="shared" ref="E13:G13" si="1">STDEV(E2:E11)</f>
         <v>47.986318652067702</v>
@@ -1049,9 +1048,9 @@
       <c r="A14" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
       <c r="E14" s="4">
         <f t="shared" ref="E14:G14" si="2">E13/SQRT(10)</f>
         <v>15.1746063467155</v>
@@ -1306,9 +1305,9 @@
       <c r="A26" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B26" s="6"/>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
       <c r="E26" s="4">
         <f t="shared" ref="E26:G26" si="3">AVERAGE(E16:E25)</f>
         <v>133.28</v>
@@ -1326,9 +1325,9 @@
       <c r="A27" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
       <c r="E27" s="4">
         <f t="shared" ref="E27:G27" si="4">STDEV(E16:E25)</f>
         <v>12.471015284339201</v>
@@ -1346,9 +1345,9 @@
       <c r="A28" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B28" s="6"/>
-      <c r="C28" s="6"/>
-      <c r="D28" s="6"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
       <c r="E28" s="4">
         <f t="shared" ref="E28:G28" si="5">E27/SQRT(10)</f>
         <v>3.9436813033284301</v>
@@ -1740,9 +1739,9 @@
       <c r="A46" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B46" s="6"/>
-      <c r="C46" s="6"/>
-      <c r="D46" s="6"/>
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
       <c r="E46" s="4">
         <f t="shared" ref="E46:G46" si="6">AVERAGE(E30:E45)</f>
         <v>53.762500000000003</v>
@@ -1760,9 +1759,9 @@
       <c r="A47" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B47" s="6"/>
-      <c r="C47" s="6"/>
-      <c r="D47" s="6"/>
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
       <c r="E47" s="4">
         <f t="shared" ref="E47:G47" si="7">STDEV(E30:E45)</f>
         <v>31.7051389104879</v>
@@ -1780,9 +1779,9 @@
       <c r="A48" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B48" s="6"/>
-      <c r="C48" s="6"/>
-      <c r="D48" s="6"/>
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
       <c r="E48" s="4">
         <f t="shared" ref="E48:G48" si="8">E47/SQRT(16)</f>
         <v>7.9262847276219697</v>
@@ -2128,9 +2127,9 @@
       <c r="A64" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B64" s="6"/>
-      <c r="C64" s="6"/>
-      <c r="D64" s="6"/>
+      <c r="B64" s="2"/>
+      <c r="C64" s="2"/>
+      <c r="D64" s="2"/>
       <c r="E64" s="4">
         <f t="shared" ref="E64:G64" si="9">AVERAGE(E50:E63)</f>
         <v>72.728571428571399</v>
@@ -2148,9 +2147,9 @@
       <c r="A65" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B65" s="6"/>
-      <c r="C65" s="6"/>
-      <c r="D65" s="6"/>
+      <c r="B65" s="2"/>
+      <c r="C65" s="2"/>
+      <c r="D65" s="2"/>
       <c r="E65" s="4">
         <f t="shared" ref="E65:G65" si="10">STDEV(E50:E63)</f>
         <v>32.129172666966298</v>
@@ -2168,9 +2167,9 @@
       <c r="A66" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B66" s="6"/>
-      <c r="C66" s="6"/>
-      <c r="D66" s="6"/>
+      <c r="B66" s="2"/>
+      <c r="C66" s="2"/>
+      <c r="D66" s="2"/>
       <c r="E66" s="4">
         <f t="shared" ref="E66:G66" si="11">E65/SQRT(14)</f>
         <v>8.5868825885921396</v>
@@ -2378,9 +2377,9 @@
       <c r="A76" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B76" s="6"/>
-      <c r="C76" s="6"/>
-      <c r="D76" s="6"/>
+      <c r="B76" s="2"/>
+      <c r="C76" s="2"/>
+      <c r="D76" s="2"/>
       <c r="E76" s="4">
         <f t="shared" ref="E76:G76" si="12">AVERAGE(E68:E75)</f>
         <v>49.6</v>
@@ -2398,9 +2397,9 @@
       <c r="A77" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B77" s="6"/>
-      <c r="C77" s="6"/>
-      <c r="D77" s="6"/>
+      <c r="B77" s="2"/>
+      <c r="C77" s="2"/>
+      <c r="D77" s="2"/>
       <c r="E77" s="4">
         <f t="shared" ref="E77:G77" si="13">STDEV(E68:E75)</f>
         <v>36.437029830340798</v>
@@ -2418,9 +2417,9 @@
       <c r="A78" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B78" s="6"/>
-      <c r="C78" s="6"/>
-      <c r="D78" s="6"/>
+      <c r="B78" s="2"/>
+      <c r="C78" s="2"/>
+      <c r="D78" s="2"/>
       <c r="E78" s="4">
         <f t="shared" ref="E78:G78" si="14">E77/SQRT(8)</f>
         <v>12.882435439665199</v>
@@ -2651,9 +2650,6 @@
       <c r="A89" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B89" s="7"/>
-      <c r="C89" s="7"/>
-      <c r="D89" s="7"/>
       <c r="E89" s="4">
         <f t="shared" ref="E89:G89" si="15">AVERAGE(E80:E88)</f>
         <v>52.488888888888901</v>
@@ -2671,9 +2667,6 @@
       <c r="A90" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B90" s="7"/>
-      <c r="C90" s="7"/>
-      <c r="D90" s="7"/>
       <c r="E90" s="4">
         <f t="shared" ref="E90:G90" si="16">STDEV(E80:E88)</f>
         <v>42.054055822371197</v>
@@ -2691,9 +2684,6 @@
       <c r="A91" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B91" s="7"/>
-      <c r="C91" s="7"/>
-      <c r="D91" s="7"/>
       <c r="E91" s="4">
         <f t="shared" ref="E91:G91" si="17">E90/SQRT(9)</f>
         <v>14.018018607457099</v>
